--- a/tables/State.xlsx
+++ b/tables/State.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.38" customWidth="1" min="1" max="1"/>
@@ -461,7 +461,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>한 행 = 상태 하나. Key는 애니메이터 상태 이름(영어, 겹치지 않음). Common Y = 10/28 회의의 공통 상태. Player·Monster·Boss Y = 그 유닛이 씀.</t>
+          <t>한 행 = 상태 하나. Key는 애니메이터 상태 이름(영어, 겹치지 않음). Common Y = 전 유닛이 확실히 가지는 공통 상태만(10/29). Player·Monster·Boss Y = 그 유닛이 씀. 몬스터는 스킬 없음. Stun은 전 유닛 공통 상태이상.</t>
         </is>
       </c>
       <c r="C1" s="1" t="n"/>
@@ -846,7 +846,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1457,6 +1457,256 @@
       <c r="J24" s="3" t="inlineStr">
         <is>
           <t>무기별 획득 모션(완성판 위주)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>10019</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>스턴</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Stun</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>공통 상태이상(전 유닛). 원인은 지게귀 벽 충돌 800ms 외 미정</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>10020</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>스킬2</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Skill2</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>플레이어 전용</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>10021</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>스킬3</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Skill3</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>플레이어 전용</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>10022</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>결박</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Bound</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>플레이어 전용. 일단 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>10023</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>페이즈 전환</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>PhaseChange</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>보스 전용</t>
         </is>
       </c>
     </row>

--- a/tables/State.xlsx
+++ b/tables/State.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.38" customWidth="1" min="1" max="1"/>
@@ -586,11 +586,6 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
           <t>Note</t>
         </is>
       </c>
@@ -634,11 +629,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -679,11 +669,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -726,11 +711,6 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
           <t>플레이어 300ms 후 무적 600ms. 슈퍼아머 중엔 생략</t>
         </is>
       </c>
@@ -774,11 +754,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -821,11 +796,6 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
           <t>보스 어택 2-1 수정 예정</t>
         </is>
       </c>
@@ -869,11 +839,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -916,11 +881,6 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
           <t>회피 확률 발동 시 모션. 구르기와 별개</t>
         </is>
       </c>
@@ -964,11 +924,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -1011,11 +966,6 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
           <t>플레이어 = 결박 가르기</t>
         </is>
       </c>
@@ -1061,11 +1011,6 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
           <t>10/28 필수. 자동 잡기</t>
         </is>
       </c>
@@ -1111,11 +1056,6 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
           <t>선택. 5타일 이상 낙하 시 200ms</t>
         </is>
       </c>
@@ -1161,11 +1101,6 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
           <t>조작 회피. 무적 300ms</t>
         </is>
       </c>
@@ -1209,11 +1144,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -1256,11 +1186,6 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
           <t>체세 0</t>
         </is>
       </c>
@@ -1306,11 +1231,6 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
           <t>플레이어는 실행, 대상은 당함</t>
         </is>
       </c>
@@ -1354,11 +1274,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -1401,11 +1316,6 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
           <t>800ms</t>
         </is>
       </c>
@@ -1451,11 +1361,6 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
           <t>무기별 획득 모션(완성판 위주)</t>
         </is>
       </c>
@@ -1501,11 +1406,6 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
           <t>공통 상태이상(전 유닛). 원인은 지게귀 벽 충돌 800ms 외 미정</t>
         </is>
       </c>
@@ -1551,11 +1451,6 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
           <t>플레이어 전용</t>
         </is>
       </c>
@@ -1601,11 +1496,6 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
           <t>플레이어 전용</t>
         </is>
       </c>
@@ -1651,11 +1541,6 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
           <t>플레이어 전용. 일단 유지</t>
         </is>
       </c>
@@ -1700,11 +1585,6 @@
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>보스 전용</t>
         </is>

--- a/tables/State.xlsx
+++ b/tables/State.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>상태 목록과 유닛별 사용 여부.</t>
+          <t>CSV,상태 목록과 유닛별 사용 여부.</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>

--- a/tables/State.xlsx
+++ b/tables/State.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>상태 머신과 Attack.StateID가 이 ID로 가리킨다.</t>
+          <t>상태 머신과 Skill.StateID·PlayerState.StateID가 이 ID로 가리킨다.</t>
         </is>
       </c>
       <c r="C3" s="1" t="n"/>

--- a/tables/State.xlsx
+++ b/tables/State.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>CSV,상태 목록과 유닛별 사용 여부.</t>
+          <t>CSV,애니메이션 상태 Key 등록 목록. 실제로 쓰는 것은 Key를 등록해 자동 배포하는 것뿐, 나머지 열은 참고용. 상태 동작은 코드로 구현(10/29).</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -497,7 +497,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>상태 머신과 Skill.StateID·PlayerState.StateID가 이 ID로 가리킨다.</t>
+          <t>개발자가 애니메이션 Key를 여기에 등록하면 자동 배포된다. 동작은 코드. Skill.StateID·PlayerState.StateID가 이 ID를 가리킴. UnitState(PlayerState·EliteState·BossState)는 다른 것: 유닛별 상태 단계·상태이상 값을 담는 JSON이고, 그 StateID가 이 목록을 가리킴.</t>
         </is>
       </c>
       <c r="C3" s="1" t="n"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>유닛마다 필요한 상태·애니메이션을 한눈에 맞추기 위해.</t>
+          <t>유닛마다 필요한 상태·애니메이션을 한눈에 맞추기 위해. 나중에 개발 단계에서 특수 상태만 따로 JSON으로 만들어 씀(10/29).</t>
         </is>
       </c>
       <c r="C4" s="1" t="n"/>

--- a/tables/State.xlsx
+++ b/tables/State.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>한 행 = 상태 하나. Key는 애니메이터 상태 이름(영어, 겹치지 않음). Common Y = 전 유닛이 확실히 가지는 공통 상태만(10/29). Player·Monster·Boss Y = 그 유닛이 씀. 몬스터는 스킬 없음. Stun은 전 유닛 공통 상태이상.</t>
+          <t>한 행 = 상태 하나. Key는 애니메이터 상태 이름(영어, 격치지 않음). Key는 프로젝트에서 Enum 관리형 데이터로 사용하기 위해서만 사용한다(10/29). Common·Player·Monster·Boss·Required 열은 사용하지 않음(참고용, 5행 비고에 넣어 추출에서 빠짐).</t>
         </is>
       </c>
       <c r="C1" s="1" t="n"/>
@@ -533,7 +533,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>Name, Note</t>
+          <t>Name, Common, Player, Monster, Boss, Required, Note</t>
         </is>
       </c>
       <c r="C5" s="1" t="n"/>
